--- a/src/main/resources/templates/Notes.xlsx
+++ b/src/main/resources/templates/Notes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10714"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Worspace\pilpose\pilpose-back\src\main\resources\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/omarbenhamida/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5950359F-0B09-456D-96FA-2F3D3AB60AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1088EC8-94DC-C647-BDBF-043445EEEF36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="740" yWindow="740" windowWidth="21600" windowHeight="11300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Référence</t>
   </si>
@@ -40,6 +40,9 @@
   </si>
   <si>
     <t>Statut</t>
+  </si>
+  <si>
+    <t>Chantier</t>
   </si>
 </sst>
 </file>
@@ -383,17 +386,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" customWidth="1"/>
-    <col min="3" max="3" width="22.42578125" customWidth="1"/>
-    <col min="4" max="4" width="23.5703125" customWidth="1"/>
-    <col min="5" max="5" width="27.42578125" customWidth="1"/>
+    <col min="1" max="1" width="17.5" customWidth="1"/>
+    <col min="2" max="2" width="16.1640625" customWidth="1"/>
+    <col min="3" max="3" width="22.5" customWidth="1"/>
+    <col min="4" max="4" width="23.5" customWidth="1"/>
+    <col min="5" max="5" width="27.5" customWidth="1"/>
+    <col min="6" max="6" width="27.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -408,6 +412,9 @@
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
